--- a/testbuild/observations-summary.xlsx
+++ b/testbuild/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="50">
   <si>
     <t>Profile</t>
   </si>
@@ -113,16 +113,19 @@
     <t>dateTime, Period, Timing, instant</t>
   </si>
   <si>
+    <t>CodeableConceptĵ</t>
+  </si>
+  <si>
+    <t>vkp-Observation-Consciousness</t>
+  </si>
+  <si>
+    <t>Vkp Observation - Consciousness</t>
+  </si>
+  <si>
+    <t>null#1104441000000107</t>
+  </si>
+  <si>
     <t>Quantity, CodeableConcept, string, boolean, integer, Range, Ratio, SampledData, time, dateTime, Period</t>
-  </si>
-  <si>
-    <t>vkp-Observation-Consciousness</t>
-  </si>
-  <si>
-    <t>Vkp Observation - Consciousness</t>
-  </si>
-  <si>
-    <t>null#1104441000000107</t>
   </si>
   <si>
     <t>vkp-Observation-Heartrate</t>
@@ -563,7 +566,7 @@
         <v>32</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>19</v>
@@ -577,10 +580,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C9" t="s" s="2">
         <v>13</v>
@@ -589,7 +592,7 @@
         <v>14</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>16</v>
@@ -612,10 +615,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s" s="2">
         <v>14</v>
@@ -624,7 +627,7 @@
         <v>14</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>31</v>
@@ -633,7 +636,7 @@
         <v>32</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>19</v>
@@ -647,10 +650,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s" s="2">
         <v>13</v>
@@ -659,7 +662,7 @@
         <v>14</v>
       </c>
       <c r="E11" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F11" t="s" s="2">
         <v>16</v>
@@ -682,10 +685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C12" t="s" s="2">
         <v>13</v>
@@ -694,7 +697,7 @@
         <v>14</v>
       </c>
       <c r="E12" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F12" t="s" s="2">
         <v>16</v>
